--- a/human_validation/judge/kor/judge_D001_S003_P002__qwen3-235b_kor.xlsx
+++ b/human_validation/judge/kor/judge_D001_S003_P002__qwen3-235b_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -561,12 +558,82 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요, 클리닉에 오신 것을 환영합니다. 저는 [이름] 선생님입니다. 오늘 어떤 일로 찾아오셨는지 말씀해 주시겠어요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 집중을 유지하는 게 어려워서 왔어요, 특히 직장에서요. 안전 브리핑이나 도면 검토를 시작할 때는 정말 집중하려고 하는데, 몇 분 지나면 벌써 머릿속이 다른 현장 문제 세 가지로 옮겨가 있어요. 그러다 제가 챙겼어야 할 걸 놓쳤다는 걸 깨닫게 돼요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 이런 집중력 문제가 평생 있어 오신 건가요, 아니면 최근에 시작된 건가요? 예를 들어 학교나 이전 직장에서는 집중력이 어땠나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 제가 기억하는 한 계속 이래왔어요. 초등학교 때 선생님들이 벌써 부모님께 제가 자리에 가만히 못 앉아 있고, 순서 안 지키고 말하고, 숙제를 잃어버린다고 말씀하셨어요. 뭘 해야 하는지 제대로 이해하기도 전에 지시사항을 서둘러 넘겨버리던 것도 기억나요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 직장 밖에서도, 예를 들어 집이나 사교 활동 중에도 산만해지거나 충동적으로 행동하시는 걸 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 네. 직장에서만 그런 게 아니에요. 집에서는 아내가 제가 하겠다고 한 일들을 계속 반복해서 상기시켜줘야 해요. 아내도 많이 지친 상태고요. 그리고 직장에서도 심각해졌어요, 후속 처리를 놓치고 현장 조율이 잘 안 된 일 때문에 회사에서 정식으로 문제 제기가 있었거든요. 솔직히 창피해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (부주의 우세형) (D002) | 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>진단명: 주의력결핍 과잉행동장애 (복합형) (D001)
 인구통계: 성별 남성 / 나이 40 / 직업상태 construction manager / 최종학력 고등학교 졸업
@@ -575,140 +642,46 @@
 증상 지속 기간: 2 years and 2 months
 추가 요건: Onset prior to age 12 years
 주호소 증상 코드: S002
-배경 서술: 2년 2개월 전, 윌리는 대규모 복합 개발 현장을 맡으면서 새벽 현장 점검, 늦은 시간의 BIM 조율 회의, 주말 점검, 끊임없는 전화 응대가 겹치는 일정으로 근무 스케줄이 바뀌었다. 이런 환경에서 오래전부터 있었던 불안정한 집중력과 충동적인 의사소통 습관이 임상적으로 문제가 될 만큼 심해졌다. 그는 안전 브리핑 시간 내내 앉아 있는 것을 힘들어했고, 하도급업체 직원들의 말을 자르며 끼어들었으며, 질문이 끝나기도 전에 결정을 불쑥 내뱉었고, 필요한 도면이나 메모를 잃어버렸으며, 예산과 현장 조율이라는 중요한 업무임에도 후속 작업을 마무리하거나 정리하지 못하는 일이 반복됐다. 지시사항을 놓치고 현장 업무를 마무리하지 못하는 일이 이어지면서 정식으로 문제가 제기되었고, 윌리는 산업보건 상담을 통해 정신건강의학과 의뢰에 동의했다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요, 클리닉에 오신 것을 환영합니다. 저는 [이름] 선생님입니다. 오늘 어떤 일로 찾아오셨는지 말씀해 주시겠어요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 집중을 유지하는 게 어려워서 왔어요, 특히 직장에서요. 안전 브리핑이나 도면 검토를 시작할 때는 정말 집중하려고 하는데, 몇 분 지나면 벌써 머릿속이 다른 현장 문제 세 가지로 옮겨가 있어요. 그러다 제가 챙겼어야 할 걸 놓쳤다는 걸 깨닫게 돼요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 이런 집중력 문제가 평생 있어 오신 건가요, 아니면 최근에 시작된 건가요? 예를 들어 학교나 이전 직장에서는 집중력이 어땠나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 제가 기억하는 한 계속 이래왔어요. 초등학교 때 선생님들이 벌써 부모님께 제가 자리에 가만히 못 앉아 있고, 순서 안 지키고 말하고, 숙제를 잃어버린다고 말씀하셨어요. 뭘 해야 하는지 제대로 이해하기도 전에 지시사항을 서둘러 넘겨버리던 것도 기억나요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 직장 밖에서도, 예를 들어 집이나 사교 활동 중에도 산만해지거나 충동적으로 행동하시는 걸 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 네. 직장에서만 그런 게 아니에요. 집에서는 아내가 제가 하겠다고 한 일들을 계속 반복해서 상기시켜줘야 해요. 아내도 많이 지친 상태고요. 그리고 직장에서도 심각해졌어요, 후속 처리를 놓치고 현장 조율이 잘 안 된 일 때문에 회사에서 정식으로 문제 제기가 있었거든요. 솔직히 창피해요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
+배경 서술: 2년 2개월 전, 윌리는 대규모 복합 개발 현장을 맡으면서 새벽 현장 점검, 늦은 시간의 BIM 조율 회의, 주말 점검, 끊임없는 전화 응대가 겹치는 일정으로 근무 스케줄이 바뀌었다. 이런 환경에서 오래전부터 있었던 불안정한 집중력과 충동적인 의사소통 습관이 임상적으로 문제가 될 만큼 심해졌다. 그는 안전 브리핑 시간 내내 앉아 있는 것을 힘들어했고, 하도급업체 직원들의 말을 자르며 끼어들었으며, 질문이 끝나기도 전에 결정을 불쑥 내뱉었고, 필요한 도면이나 메모를 잃어버렸으며, 예산과 현장 조율이라는 중요한 업무임에도 후속 작업을 마무리하거나 정리하지 못하는 일이 반복됐다. 지시사항을 놓치고 현장 업무를 마무리하지 못하는 일이 이어지면서 정식으로 문제가 제기되었고, 윌리는 산업보건 상담을 통해 정신건강의학과 의뢰에 동의했다.
+표집된 증상 목록:
+  - S002 지속적 주의 유지 곤란: 과제나 놀이 활동에서 주의를 지속하는 데 자주 어려움을 겪는다.
+  - S003 경청 곤란: 직접 말을 걸어도 듣지 않는 것처럼 보이는 경우가 잦다.
+  - S004 지시 이행 곤란: 지시를 끝까지 따르지 못하고 학업, 집안일, 직장 업무를 제대로 마치지 못하는 경우가 잦다.
+  - S005 조직화 곤란: 과제와 활동을 체계적으로 조직하는 데 자주 어려움을 겪는다.
+  - S007 물건 분실: 과제나 활동에 필요한 물건을 자주 잃어버린다.
+  - S011 자리 이탈: 가만히 앉아 있어야 하는 상황에서 자주 자리를 떠난다.
+  - S015 과도한 말하기: 지나치게 말을 많이 하는 경우가 잦다.
+  - S016 성급한 대답: 질문이 끝나기도 전에 불쑥 대답해버리는 경우가 잦다.
+  - S017 차례 기다리기 곤란: 차례를 기다리는 데 자주 어려움을 겪는다.
+  - S018 끼어들기/방해: 다른 사람의 대화나 활동에 자주 끼어들거나 방해한다(예: 대화, 게임, 활동에 불쑥 끼어듦).</t>
+        </is>
+      </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>[3번째 턴 · 의사의 감별진단] 고확률: 주의력결핍 과잉행동장애 (부주의 우세형) (D002) | 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: 주의력결핍 과잉행동장애 (부주의 우세형) (D002, ICD: F90.0)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: inattention (관계=must_include, 요구개수=5, 충족개수=5, 커버리지=1.0)
-  확인된 근거: 세부사항 부주의 실수: 세부적인 것에 주의를 기울이지 못하거나 부주의한 실수를 자주 한다.; 지속적 주의 유지 곤란: 과제나 놀이 활동에서 주의를 지속하는 데 자주 어려움을 겪는다.; 조직화 곤란: 과제와 활동을 체계적으로 조직하는 데 자주 어려움을 겪는다.; 물건 분실: 과제나 활동에 필요한 물건을 자주 잃어버린다.; 일상 활동 망각: 일상 활동에서 자주 잊어버린다(예: 집안일, 심부름, 성인의 경우 전화 회신, 청구서 납부, 약속 지키기 등).
-  누락: 경청 곤란: 직접 말을 걸어도 듣지 않는 것처럼 보이는 경우가 잦다.; 지시 이행 곤란: 지시를 끝까지 따르지 못하고 학업, 집안일, 직장 업무를 제대로 마치지 못하는 경우가 잦다.; 지속적 정신적 노력 회피: 지속적인 정신적 노력을 요하는 과제를 자주 피하거나 싫어하거나 꺼린다.; 산만함: 외부 자극에 의해 쉽게 주의가 분산된다(청소년 후기 및 성인의 경우 관련 없는 생각도 포함될 수 있다).</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: hyperactivity_impulsivity (관계=must_include, 요구개수=5, 충족개수=2, 커버리지=0.4)
-  확인된 근거: 자리 이탈: 가만히 앉아 있어야 하는 상황에서 자주 자리를 떠난다.; 성급한 대답: 질문이 끝나기도 전에 불쑥 대답해버리는 경우가 잦다.
-  누락: 손발 꼼지락거림: 손발을 가만두지 못하고 두드리거나 자리에서 꼼지락거리는 경우가 잦다.; 안절부절못함: 부적절한 상황에서 자주 뛰어다니거나 기어오른다(청소년/성인의 경우 안절부절못하는 느낌으로 제한될 수 있다).; 조용한 활동 곤란: 여가 활동을 조용히 하지 못하는 경우가 잦다.; 끊임없는 활동성: 마치 '모터가 달린 것처럼' 끊임없이 활동한다.; 과도한 말하기: 지나치게 말을 많이 하는 경우가 잦다.; 차례 기다리기 곤란: 차례를 기다리는 데 자주 어려움을 겪는다.; 끼어들기/방해: 다른 사람의 대화나 활동에 자주 끼어들거나 방해한다(예: 대화, 게임, 활동에 불쑥 끼어듦).</t>
+          <t>의사의 최종 진단: 주의력결핍 과잉행동장애 (부주의 우세형) (D002, ICD: F90.0)
+지속 기간 요건: 있음
+기능적 손상 요건: 있음
+추가 요건: 있음
+체크리스트 그룹: inattention (관계=must_include, 요구개수=5, 충족개수=5, 커버리지=1.0)
+확인된 근거:
+  - 세부사항 부주의 실수: 세부적인 것에 주의를 기울이지 못하거나 부주의한 실수를 자주 한다.
+  - 지속적 주의 유지 곤란: 과제나 놀이 활동에서 주의를 지속하는 데 자주 어려움을 겪는다.
+  - 조직화 곤란: 과제와 활동을 체계적으로 조직하는 데 자주 어려움을 겪는다.
+  - 물건 분실: 과제나 활동에 필요한 물건을 자주 잃어버린다.
+  - 일상 활동 망각: 일상 활동에서 자주 잊어버린다(예: 집안일, 심부름, 성인의 경우 전화 회신, 청구서 납부, 약속 지키기 등).
+체크리스트 그룹: hyperactivity_impulsivity (관계=must_include, 요구개수=5, 충족개수=2, 커버리지=0.4)
+확인된 근거:
+  - 자리 이탈: 가만히 앉아 있어야 하는 상황에서 자주 자리를 떠난다.
+  - 성급한 대답: 질문이 끝나기도 전에 불쑥 대답해버리는 경우가 잦다.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A25:B25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D001_S003_P002__qwen3-235b_kor.xlsx
+++ b/human_validation/judge/kor/judge_D001_S003_P002__qwen3-235b_kor.xlsx
@@ -628,6 +628,11 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -677,11 +682,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A25:B25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D001_S003_P002__qwen3-235b_kor.xlsx
+++ b/human_validation/judge/kor/judge_D001_S003_P002__qwen3-235b_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -472,7 +473,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.2222</v>
+        <v>0.2889</v>
       </c>
     </row>
     <row r="5">
@@ -492,7 +493,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.3333</v>
+        <v>0.4444</v>
       </c>
     </row>
     <row r="7">
@@ -502,7 +503,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="8">
@@ -555,6 +556,7 @@
         <v>0.875</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
